--- a/05. Res/modelos/sobredispersion_poisson.xlsx
+++ b/05. Res/modelos/sobredispersion_poisson.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">modelo</t>
   </si>
@@ -29,13 +29,16 @@
     <t xml:space="preserve">p_valor</t>
   </si>
   <si>
-    <t xml:space="preserve">interpretacion</t>
+    <t xml:space="preserve">indicador_sobredispersion_moderada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indicador_sobredispersion_importante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indicador_subdispersion</t>
   </si>
   <si>
     <t xml:space="preserve">Poisson frecuencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidencia moderada de sobredispersion</t>
   </si>
 </sst>
 </file>
@@ -83,15 +86,17 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:F2" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F2"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H2" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H2"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="modelo"/>
     <tableColumn id="2" name="chi_cuadrado_pearson"/>
     <tableColumn id="3" name="gl"/>
     <tableColumn id="4" name="ratio_sobredispersion"/>
     <tableColumn id="5" name="p_valor"/>
-    <tableColumn id="6" name="interpretacion"/>
+    <tableColumn id="6" name="indicador_sobredispersion_moderada"/>
+    <tableColumn id="7" name="indicador_sobredispersion_importante"/>
+    <tableColumn id="8" name="indicador_subdispersion"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -398,25 +403,37 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>118660.028911188</v>
+        <v>119860.774838877</v>
       </c>
       <c r="C2" t="n">
-        <v>84318</v>
+        <v>84230</v>
       </c>
       <c r="D2" t="n">
-        <v>1.40729178717697</v>
+        <v>1.4230176283851</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="s">
-        <v>7</v>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
